--- a/data/trans_orig/P21D6_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D6_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención fisioterapéutica en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención fisioterapéutica en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>209856</t>
+          <t>209806</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>222345</t>
+          <t>222296</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>283705</t>
+          <t>284127</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>301406</t>
+          <t>301836</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>499481</t>
+          <t>499818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>521364</t>
+          <t>520951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18673</t>
+          <t>19150</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18780</t>
+          <t>19124</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32520</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28483</t>
+          <t>28898</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46654</t>
+          <t>46605</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6760</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15864</t>
+          <t>15809</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15545</t>
+          <t>15902</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11980</t>
+          <t>12885</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4486</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14248</t>
+          <t>13597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>405123</t>
+          <t>404883</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>999607</t>
+          <t>996950</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>802682</t>
+          <t>802215</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>849830</t>
+          <t>849693</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1112635</t>
+          <t>1040318</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1820768</t>
+          <t>1820399</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83246</t>
+          <t>86369</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>689335</t>
+          <t>699488</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62499</t>
+          <t>61621</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100117</t>
+          <t>99258</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>168455</t>
+          <t>166132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>901127</t>
+          <t>956676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>46,59%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39465</t>
+          <t>39863</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13498</t>
+          <t>13765</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30084</t>
+          <t>29902</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27387</t>
+          <t>26196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59851</t>
+          <t>59695</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14541</t>
+          <t>14458</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>6562</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20015</t>
+          <t>20182</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28049</t>
+          <t>26837</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>237167</t>
+          <t>239449</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>268082</t>
+          <t>267943</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>250966</t>
+          <t>251219</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>274007</t>
+          <t>274049</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>499752</t>
+          <t>497920</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>536898</t>
+          <t>536875</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33458</t>
+          <t>33165</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61204</t>
+          <t>60980</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31687</t>
+          <t>31963</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51152</t>
+          <t>51869</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>69315</t>
+          <t>70084</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>104276</t>
+          <t>105933</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15655</t>
+          <t>15865</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17798</t>
+          <t>19524</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25349</t>
+          <t>25442</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>518</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6661</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>715262</t>
+          <t>720802</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1464915</t>
+          <t>1465182</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1356147</t>
+          <t>1355875</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1414649</t>
+          <t>1411978</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1931548</t>
+          <t>1954634</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2850146</t>
+          <t>2851696</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,94%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>148010</t>
+          <t>146145</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>920463</t>
+          <t>912340</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>122545</t>
+          <t>121750</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>167902</t>
+          <t>169545</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>290301</t>
+          <t>288925</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1238985</t>
+          <t>1208576</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,27%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>16706</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>48512</t>
+          <t>45840</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28487</t>
+          <t>28596</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50928</t>
+          <t>52277</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>47802</t>
+          <t>47722</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>88019</t>
+          <t>87717</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17330</t>
+          <t>16869</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13534</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28248</t>
+          <t>28812</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>19371</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42106</t>
+          <t>40582</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D6_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D6_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>217164</t>
+          <t>238861</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>209806</t>
+          <t>231353</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>222296</t>
+          <t>244407</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>293583</t>
+          <t>316687</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>284127</t>
+          <t>306107</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>301836</t>
+          <t>324686</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>510746</t>
+          <t>555548</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>499818</t>
+          <t>542734</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>520951</t>
+          <t>566488</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,08%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>12796</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19150</t>
+          <t>20751</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25165</t>
+          <t>27146</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19124</t>
+          <t>21120</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32181</t>
+          <t>35623</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>37094</t>
+          <t>39942</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28898</t>
+          <t>31213</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46605</t>
+          <t>50414</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15809</t>
+          <t>16566</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6190</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15902</t>
+          <t>16798</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12885</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13597</t>
+          <t>14715</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>230097</t>
+          <t>252652</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230097</t>
+          <t>252652</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>230097</t>
+          <t>252652</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>336627</t>
+          <t>362528</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>336627</t>
+          <t>362528</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336627</t>
+          <t>362528</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>566724</t>
+          <t>615180</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>566724</t>
+          <t>615180</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>566724</t>
+          <t>615180</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>770476</t>
+          <t>852633</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>404883</t>
+          <t>829115</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>996950</t>
+          <t>874326</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>822680</t>
+          <t>859614</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>802215</t>
+          <t>837540</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>849693</t>
+          <t>877387</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1593156</t>
+          <t>1712246</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1040318</t>
+          <t>1679484</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1820399</t>
+          <t>1741108</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>89,56%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>318428</t>
+          <t>77082</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86369</t>
+          <t>59021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>699488</t>
+          <t>99028</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>82268</t>
+          <t>90407</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61621</t>
+          <t>74739</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99258</t>
+          <t>107250</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>400696</t>
+          <t>167489</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>166132</t>
+          <t>143732</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>956676</t>
+          <t>196979</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21290</t>
+          <t>22887</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39863</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20436</t>
+          <t>22902</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13765</t>
+          <t>15702</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29902</t>
+          <t>32852</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>41726</t>
+          <t>45788</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26196</t>
+          <t>34164</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59695</t>
+          <t>61200</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14458</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>12596</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20182</t>
+          <t>19923</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>17838</t>
+          <t>18502</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>12025</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26837</t>
+          <t>28840</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1116103</t>
+          <t>958507</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1116103</t>
+          <t>958507</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1116103</t>
+          <t>958507</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2053416</t>
+          <t>1944025</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2053416</t>
+          <t>1944025</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2053416</t>
+          <t>1944025</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>254798</t>
+          <t>287926</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>239449</t>
+          <t>270437</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>267943</t>
+          <t>303557</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>264446</t>
+          <t>291557</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>251219</t>
+          <t>279261</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>274049</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>519245</t>
+          <t>579482</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>497920</t>
+          <t>556905</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>536875</t>
+          <t>597849</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45773</t>
+          <t>49451</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33165</t>
+          <t>35211</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60980</t>
+          <t>66168</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40297</t>
+          <t>43393</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31963</t>
+          <t>33470</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51869</t>
+          <t>54849</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>86070</t>
+          <t>92843</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>70084</t>
+          <t>76002</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>105933</t>
+          <t>113082</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15865</t>
+          <t>17393</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7030</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19524</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14957</t>
+          <t>14883</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8469</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25442</t>
+          <t>25135</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>510</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>506</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1242439</t>
+          <t>1379420</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>720802</t>
+          <t>1350499</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1465182</t>
+          <t>1408191</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1380709</t>
+          <t>1467856</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1355875</t>
+          <t>1443068</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1411978</t>
+          <t>1491247</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2623148</t>
+          <t>2847276</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1954634</t>
+          <t>2808912</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2851696</t>
+          <t>2883863</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>376130</t>
+          <t>139328</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>146145</t>
+          <t>113583</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>912340</t>
+          <t>165600</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>147729</t>
+          <t>160946</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>121750</t>
+          <t>141609</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>169545</t>
+          <t>183514</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>523860</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>288925</t>
+          <t>269526</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1208576</t>
+          <t>332441</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -2658,102 +2658,102 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29217</t>
+          <t>30989</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16706</t>
+          <t>20591</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45840</t>
+          <t>47075</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>40555</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>31492</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>54825</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>71543</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>57146</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>91371</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>1,76%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>37868</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>28596</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>52277</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>67086</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>47722</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>87717</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16869</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13431</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28812</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,27 +2841,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>29560</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40582</t>
+          <t>40502</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1656384</t>
+          <t>1558368</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1656384</t>
+          <t>1558368</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1656384</t>
+          <t>1558368</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1586227</t>
+          <t>1690286</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1586227</t>
+          <t>1690286</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1586227</t>
+          <t>1690286</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3242611</t>
+          <t>3248654</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3242611</t>
+          <t>3248654</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3242611</t>
+          <t>3248654</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
